--- a/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
+++ b/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/TAbaseplate2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB474367-2E2A-DB40-AB81-6F662AD9BBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454ED5A2-2142-A042-9A83-19E26DF22D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="740" windowWidth="14700" windowHeight="16680" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
+    <workbookView xWindow="19400" yWindow="740" windowWidth="10000" windowHeight="16680" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>TA_Baseplate_V2</t>
   </si>
@@ -68,9 +68,6 @@
     <t>SRS SR475 Shutter</t>
   </si>
   <si>
-    <t>Taboard</t>
-  </si>
-  <si>
     <t>cube_mount_halfinch.step</t>
   </si>
   <si>
@@ -92,10 +89,31 @@
     <t>IO-3D-780-VLP</t>
   </si>
   <si>
-    <t>circular_lens (f = 150 mm)</t>
-  </si>
-  <si>
     <t>BB05-E03</t>
+  </si>
+  <si>
+    <t>TA_Baseplate_V2.step</t>
+  </si>
+  <si>
+    <t>Surface_Adapter_aom.step</t>
+  </si>
+  <si>
+    <t>Iris_Mount.step</t>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>SM05L05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SM05FCA2 </t>
+  </si>
+  <si>
+    <t>S05TM09</t>
+  </si>
+  <si>
+    <t>LA1614-B</t>
   </si>
 </sst>
 </file>
@@ -140,12 +158,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -481,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE4F86D-9124-0842-A565-85DDB1A301A8}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
@@ -511,7 +532,7 @@
     </row>
     <row r="5" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -519,23 +540,23 @@
     </row>
     <row r="6" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -543,55 +564,71 @@
     </row>
     <row r="9" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1">
-        <v>7</v>
+    <row r="10" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2</v>
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B16" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>18</v>
+      <c r="A18" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -599,15 +636,15 @@
     </row>
     <row r="19" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -615,38 +652,73 @@
     </row>
     <row r="21" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="1">
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A13" r:id="rId1" xr:uid="{6E786827-FF2D-5346-88D3-375FCDA41C8E}"/>
-    <hyperlink ref="A14" r:id="rId2" xr:uid="{8390965A-7195-2A42-AF1B-5854895A15D5}"/>
-    <hyperlink ref="A19" r:id="rId3" xr:uid="{07E98017-A723-394F-B24E-732469DE3657}"/>
-    <hyperlink ref="A20" r:id="rId4" xr:uid="{B1B7AE46-E7C4-6844-9473-3E1D8717E3E2}"/>
-    <hyperlink ref="A21" r:id="rId5" xr:uid="{11E87089-7CA8-A24A-AFB4-A01880996CD6}"/>
-    <hyperlink ref="A17" r:id="rId6" xr:uid="{25EECDFE-92ED-4D4C-B62B-77D92F9D3B2C}"/>
-    <hyperlink ref="A15" r:id="rId7" xr:uid="{E5BDCA7F-2CF4-4949-9673-7DD790257BA1}"/>
-    <hyperlink ref="A16" r:id="rId8" display="circular_mirror" xr:uid="{6B7189F7-A68F-AD4D-B6FE-981634C46653}"/>
+    <hyperlink ref="A15" r:id="rId1" xr:uid="{6E786827-FF2D-5346-88D3-375FCDA41C8E}"/>
+    <hyperlink ref="A16" r:id="rId2" xr:uid="{8390965A-7195-2A42-AF1B-5854895A15D5}"/>
+    <hyperlink ref="A24" r:id="rId3" xr:uid="{07E98017-A723-394F-B24E-732469DE3657}"/>
+    <hyperlink ref="A25" r:id="rId4" xr:uid="{B1B7AE46-E7C4-6844-9473-3E1D8717E3E2}"/>
+    <hyperlink ref="A26" r:id="rId5" xr:uid="{11E87089-7CA8-A24A-AFB4-A01880996CD6}"/>
+    <hyperlink ref="A22" r:id="rId6" xr:uid="{25EECDFE-92ED-4D4C-B62B-77D92F9D3B2C}"/>
+    <hyperlink ref="A20" r:id="rId7" xr:uid="{E5BDCA7F-2CF4-4949-9673-7DD790257BA1}"/>
+    <hyperlink ref="A21" r:id="rId8" display="circular_mirror" xr:uid="{6B7189F7-A68F-AD4D-B6FE-981634C46653}"/>
+    <hyperlink ref="A17" r:id="rId9" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05L05" xr:uid="{FF78656F-8ADD-E145-B586-6AF2D518128C}"/>
+    <hyperlink ref="A18" r:id="rId10" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05FCA2" xr:uid="{F11CC66A-3DF6-1B47-BC61-CA62A77D84DB}"/>
+    <hyperlink ref="A23" r:id="rId11" xr:uid="{F1779B59-E753-EA41-89E9-6D847DAECC79}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
